--- a/outputs/45635.xlsx
+++ b/outputs/45635.xlsx
@@ -109,11 +109,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -368,19 +368,19 @@
         <v>0</v>
       </c>
       <c r="B5" s="1" t="n">
-        <f aca="false">IF(COUNTIF(B$1:B$3,MAX(B$1:B$3))=1,IF(B1=MAX(B$1:B$3),6,0),IF(COUNTIF(B$1:B$3,MAX(B$1:B$3))=2,IF(B1=MAX(B$1:B$3),3,0),IF(B1=MAX(B$1:B$3),2,0)))</f>
+        <f aca="false">IF(COUNTIF(B$1:B$3,MAX(B$1:B$3))=3,2,IF(B1=MAX(B$1:B$3),IF(COUNTIF(B$1:B$3,MAX(B$1:B$3))=2,3,6),0))</f>
         <v>6</v>
       </c>
       <c r="C5" s="1" t="n">
-        <f aca="false">IF(COUNTIF(C$1:C$3,MAX(C$1:C$3))=1,IF(C1=MAX(C$1:C$3),6,0),IF(COUNTIF(C$1:C$3,MAX(C$1:C$3))=2,IF(C1=MAX(C$1:C$3),3,0),IF(C1=MAX(C$1:C$3),2,0)))</f>
+        <f aca="false">IF(COUNTIF(C$1:C$3,MAX(C$1:C$3))=3,2,IF(C1=MAX(C$1:C$3),IF(COUNTIF(C$1:C$3,MAX(C$1:C$3))=2,3,6),0))</f>
         <v>3</v>
       </c>
       <c r="D5" s="1" t="n">
-        <f aca="false">IF(COUNTIF(D$1:D$3,MAX(D$1:D$3))=1,IF(D1=MAX(D$1:D$3),6,0),IF(COUNTIF(D$1:D$3,MAX(D$1:D$3))=2,IF(D1=MAX(D$1:D$3),3,0),IF(D1=MAX(D$1:D$3),2,0)))</f>
+        <f aca="false">IF(COUNTIF(D$1:D$3,MAX(D$1:D$3))=3,2,IF(D1=MAX(D$1:D$3),IF(COUNTIF(D$1:D$3,MAX(D$1:D$3))=2,3,6),0))</f>
         <v>2</v>
       </c>
       <c r="E5" s="1" t="n">
-        <f aca="false">IF(COUNTIF(E$1:E$3,MAX(E$1:E$3))=1,IF(E1=MAX(E$1:E$3),6,0),IF(COUNTIF(E$1:E$3,MAX(E$1:E$3))=2,IF(E1=MAX(E$1:E$3),3,0),IF(E1=MAX(E$1:E$3),2,0)))</f>
+        <f aca="false">IF(COUNTIF(E$1:E$3,MAX(E$1:E$3))=3,2,IF(E1=MAX(E$1:E$3),IF(COUNTIF(E$1:E$3,MAX(E$1:E$3))=2,3,6),0))</f>
         <v>0</v>
       </c>
     </row>
@@ -389,19 +389,19 @@
         <v>1</v>
       </c>
       <c r="B6" s="1" t="n">
-        <f aca="false">IF(COUNTIF(B$1:B$3,MAX(B$1:B$3))=1,IF(B2=MAX(B$1:B$3),6,0),IF(COUNTIF(B$1:B$3,MAX(B$1:B$3))=2,IF(B2=MAX(B$1:B$3),3,0),IF(B2=MAX(B$1:B$3),2,0)))</f>
+        <f aca="false">IF(COUNTIF(B$1:B$3,MAX(B$1:B$3))=3,2,IF(B2=MAX(B$1:B$3),IF(COUNTIF(B$1:B$3,MAX(B$1:B$3))=2,3,6),0))</f>
         <v>0</v>
       </c>
       <c r="C6" s="1" t="n">
-        <f aca="false">IF(COUNTIF(C$1:C$3,MAX(C$1:C$3))=1,IF(C2=MAX(C$1:C$3),6,0),IF(COUNTIF(C$1:C$3,MAX(C$1:C$3))=2,IF(C2=MAX(C$1:C$3),3,0),IF(C2=MAX(C$1:C$3),2,0)))</f>
+        <f aca="false">IF(COUNTIF(C$1:C$3,MAX(C$1:C$3))=3,2,IF(C2=MAX(C$1:C$3),IF(COUNTIF(C$1:C$3,MAX(C$1:C$3))=2,3,6),0))</f>
         <v>0</v>
       </c>
       <c r="D6" s="1" t="n">
-        <f aca="false">IF(COUNTIF(D$1:D$3,MAX(D$1:D$3))=1,IF(D2=MAX(D$1:D$3),6,0),IF(COUNTIF(D$1:D$3,MAX(D$1:D$3))=2,IF(D2=MAX(D$1:D$3),3,0),IF(D2=MAX(D$1:D$3),2,0)))</f>
+        <f aca="false">IF(COUNTIF(D$1:D$3,MAX(D$1:D$3))=3,2,IF(D2=MAX(D$1:D$3),IF(COUNTIF(D$1:D$3,MAX(D$1:D$3))=2,3,6),0))</f>
         <v>2</v>
       </c>
       <c r="E6" s="1" t="n">
-        <f aca="false">IF(COUNTIF(E$1:E$3,MAX(E$1:E$3))=1,IF(E2=MAX(E$1:E$3),6,0),IF(COUNTIF(E$1:E$3,MAX(E$1:E$3))=2,IF(E2=MAX(E$1:E$3),3,0),IF(E2=MAX(E$1:E$3),2,0)))</f>
+        <f aca="false">IF(COUNTIF(E$1:E$3,MAX(E$1:E$3))=3,2,IF(E2=MAX(E$1:E$3),IF(COUNTIF(E$1:E$3,MAX(E$1:E$3))=2,3,6),0))</f>
         <v>0</v>
       </c>
     </row>
@@ -410,19 +410,19 @@
         <v>2</v>
       </c>
       <c r="B7" s="1" t="n">
-        <f aca="false">IF(COUNTIF(B$1:B$3,MAX(B$1:B$3))=1,IF(B3=MAX(B$1:B$3),6,0),IF(COUNTIF(B$1:B$3,MAX(B$1:B$3))=2,IF(B3=MAX(B$1:B$3),3,0),IF(B3=MAX(B$1:B$3),2,0)))</f>
+        <f aca="false">IF(COUNTIF(B$1:B$3,MAX(B$1:B$3))=3,2,IF(B3=MAX(B$1:B$3),IF(COUNTIF(B$1:B$3,MAX(B$1:B$3))=2,3,6),0))</f>
         <v>0</v>
       </c>
       <c r="C7" s="1" t="n">
-        <f aca="false">IF(COUNTIF(C$1:C$3,MAX(C$1:C$3))=1,IF(C3=MAX(C$1:C$3),6,0),IF(COUNTIF(C$1:C$3,MAX(C$1:C$3))=2,IF(C3=MAX(C$1:C$3),3,0),IF(C3=MAX(C$1:C$3),2,0)))</f>
+        <f aca="false">IF(COUNTIF(C$1:C$3,MAX(C$1:C$3))=3,2,IF(C3=MAX(C$1:C$3),IF(COUNTIF(C$1:C$3,MAX(C$1:C$3))=2,3,6),0))</f>
         <v>3</v>
       </c>
       <c r="D7" s="1" t="n">
-        <f aca="false">IF(COUNTIF(D$1:D$3,MAX(D$1:D$3))=1,IF(D3=MAX(D$1:D$3),6,0),IF(COUNTIF(D$1:D$3,MAX(D$1:D$3))=2,IF(D3=MAX(D$1:D$3),3,0),IF(D3=MAX(D$1:D$3),2,0)))</f>
+        <f aca="false">IF(COUNTIF(D$1:D$3,MAX(D$1:D$3))=3,2,IF(D3=MAX(D$1:D$3),IF(COUNTIF(D$1:D$3,MAX(D$1:D$3))=2,3,6),0))</f>
         <v>2</v>
       </c>
       <c r="E7" s="1" t="n">
-        <f aca="false">IF(COUNTIF(E$1:E$3,MAX(E$1:E$3))=1,IF(E3=MAX(E$1:E$3),6,0),IF(COUNTIF(E$1:E$3,MAX(E$1:E$3))=2,IF(E3=MAX(E$1:E$3),3,0),IF(E3=MAX(E$1:E$3),2,0)))</f>
+        <f aca="false">IF(COUNTIF(E$1:E$3,MAX(E$1:E$3))=3,2,IF(E3=MAX(E$1:E$3),IF(COUNTIF(E$1:E$3,MAX(E$1:E$3))=2,3,6),0))</f>
         <v>6</v>
       </c>
     </row>

--- a/outputs/45635.xlsx
+++ b/outputs/45635.xlsx
@@ -368,20 +368,16 @@
         <v>0</v>
       </c>
       <c r="B5" s="1" t="n">
-        <f aca="false">IF(COUNTIF(B$1:B$3,MAX(B$1:B$3))=3,2,IF(B1=MAX(B$1:B$3),IF(COUNTIF(B$1:B$3,MAX(B$1:B$3))=2,3,6),0))</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C5" s="1" t="n">
-        <f aca="false">IF(COUNTIF(C$1:C$3,MAX(C$1:C$3))=3,2,IF(C1=MAX(C$1:C$3),IF(COUNTIF(C$1:C$3,MAX(C$1:C$3))=2,3,6),0))</f>
         <v>3</v>
       </c>
       <c r="D5" s="1" t="n">
-        <f aca="false">IF(COUNTIF(D$1:D$3,MAX(D$1:D$3))=3,2,IF(D1=MAX(D$1:D$3),IF(COUNTIF(D$1:D$3,MAX(D$1:D$3))=2,3,6),0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" s="1" t="n">
-        <f aca="false">IF(COUNTIF(E$1:E$3,MAX(E$1:E$3))=3,2,IF(E1=MAX(E$1:E$3),IF(COUNTIF(E$1:E$3,MAX(E$1:E$3))=2,3,6),0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -389,19 +385,15 @@
         <v>1</v>
       </c>
       <c r="B6" s="1" t="n">
-        <f aca="false">IF(COUNTIF(B$1:B$3,MAX(B$1:B$3))=3,2,IF(B2=MAX(B$1:B$3),IF(COUNTIF(B$1:B$3,MAX(B$1:B$3))=2,3,6),0))</f>
         <v>0</v>
       </c>
       <c r="C6" s="1" t="n">
-        <f aca="false">IF(COUNTIF(C$1:C$3,MAX(C$1:C$3))=3,2,IF(C2=MAX(C$1:C$3),IF(COUNTIF(C$1:C$3,MAX(C$1:C$3))=2,3,6),0))</f>
         <v>0</v>
       </c>
       <c r="D6" s="1" t="n">
-        <f aca="false">IF(COUNTIF(D$1:D$3,MAX(D$1:D$3))=3,2,IF(D2=MAX(D$1:D$3),IF(COUNTIF(D$1:D$3,MAX(D$1:D$3))=2,3,6),0))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" s="1" t="n">
-        <f aca="false">IF(COUNTIF(E$1:E$3,MAX(E$1:E$3))=3,2,IF(E2=MAX(E$1:E$3),IF(COUNTIF(E$1:E$3,MAX(E$1:E$3))=2,3,6),0))</f>
         <v>0</v>
       </c>
     </row>
@@ -410,20 +402,16 @@
         <v>2</v>
       </c>
       <c r="B7" s="1" t="n">
-        <f aca="false">IF(COUNTIF(B$1:B$3,MAX(B$1:B$3))=3,2,IF(B3=MAX(B$1:B$3),IF(COUNTIF(B$1:B$3,MAX(B$1:B$3))=2,3,6),0))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C7" s="1" t="n">
-        <f aca="false">IF(COUNTIF(C$1:C$3,MAX(C$1:C$3))=3,2,IF(C3=MAX(C$1:C$3),IF(COUNTIF(C$1:C$3,MAX(C$1:C$3))=2,3,6),0))</f>
         <v>3</v>
       </c>
       <c r="D7" s="1" t="n">
-        <f aca="false">IF(COUNTIF(D$1:D$3,MAX(D$1:D$3))=3,2,IF(D3=MAX(D$1:D$3),IF(COUNTIF(D$1:D$3,MAX(D$1:D$3))=2,3,6),0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" s="1" t="n">
-        <f aca="false">IF(COUNTIF(E$1:E$3,MAX(E$1:E$3))=3,2,IF(E3=MAX(E$1:E$3),IF(COUNTIF(E$1:E$3,MAX(E$1:E$3))=2,3,6),0))</f>
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
